--- a/FLORES DE ESTRADA/Junio/EDESUR JUNIO.xlsx
+++ b/FLORES DE ESTRADA/Junio/EDESUR JUNIO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC5E82DD-5602-489B-8E9D-FFB6924CFB6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF052AC4-377D-4177-85FF-2FA53B573A81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -330,12 +330,12 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -382,12 +382,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor theme="0"/>
       </patternFill>
     </fill>
   </fills>
@@ -549,7 +543,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -606,13 +600,10 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -622,7 +613,6 @@
     <xf numFmtId="166" fontId="4" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="8" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -630,7 +620,16 @@
     <xf numFmtId="165" fontId="4" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="12" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -646,7 +645,6 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -951,14 +949,14 @@
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="14.85546875" customWidth="1"/>
     <col min="4" max="4" width="27" customWidth="1"/>
-    <col min="5" max="5" width="6.42578125" customWidth="1"/>
+    <col min="5" max="5" width="6.5703125" customWidth="1"/>
     <col min="6" max="6" width="10.42578125" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="10" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="7.7109375" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="10.42578125" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="13.85546875" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="15.42578125" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="12.7109375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="16.5703125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="13.85546875" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="11.140625" hidden="1" customWidth="1"/>
     <col min="13" max="13" width="13.7109375" customWidth="1"/>
     <col min="14" max="14" width="13.5703125" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="13.7109375" hidden="1" customWidth="1"/>
@@ -971,21 +969,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="63"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="66"/>
       <c r="N1" s="1"/>
       <c r="O1" s="2"/>
       <c r="P1" s="3"/>
@@ -1127,7 +1125,7 @@
       <c r="B8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="68">
+      <c r="C8" s="63">
         <v>708393.51</v>
       </c>
       <c r="E8" s="10"/>
@@ -1141,7 +1139,7 @@
       <c r="M8" s="12"/>
       <c r="N8" s="3"/>
       <c r="O8" s="2"/>
-      <c r="S8" s="47"/>
+      <c r="S8" s="44"/>
     </row>
     <row r="9" spans="1:25" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
@@ -1179,7 +1177,7 @@
       </c>
       <c r="L9" s="15">
         <f>C8-J34</f>
-        <v>410809.87620000058</v>
+        <v>236778.57899999944</v>
       </c>
       <c r="M9" s="14" t="s">
         <v>19</v>
@@ -1209,10 +1207,10 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="F10" s="18">
-        <v>18022.7</v>
-      </c>
-      <c r="G10" s="41">
         <v>18321.599999999999</v>
+      </c>
+      <c r="G10" s="57">
+        <v>18790.099999999999</v>
       </c>
       <c r="H10" s="19">
         <v>0</v>
@@ -1223,31 +1221,31 @@
       </c>
       <c r="J10" s="20">
         <f>(G10-F10)*93.78</f>
-        <v>28030.841999999797</v>
+        <v>43935.93</v>
       </c>
       <c r="K10" s="21">
         <f>G10-F10</f>
-        <v>298.89999999999782</v>
+        <v>468.5</v>
       </c>
       <c r="L10" s="19">
         <f>L9*E10/100</f>
-        <v>20129.683933800032</v>
+        <v>11602.150370999972</v>
       </c>
       <c r="M10" s="19">
         <f>J10+L10+3</f>
-        <v>48163.525933799829</v>
+        <v>55541.080370999975</v>
       </c>
       <c r="N10" s="22">
         <f>J10/C7*100</f>
-        <v>35.913955156950408</v>
+        <v>56.29203074951954</v>
       </c>
       <c r="O10" s="23">
         <f>J10/L9*100</f>
-        <v>6.823312589094896</v>
+        <v>18.555703047782927</v>
       </c>
       <c r="P10" s="20">
         <f>C7*O10/100</f>
-        <v>5325.5954757885656</v>
+        <v>14482.726228794574</v>
       </c>
       <c r="Q10" s="24">
         <v>0.31</v>
@@ -1261,47 +1259,47 @@
       <c r="A11" s="18">
         <v>2</v>
       </c>
-      <c r="B11" s="55">
+      <c r="B11" s="51">
         <v>2</v>
       </c>
-      <c r="C11" s="55" t="s">
+      <c r="C11" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="55" t="s">
+      <c r="D11" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="55">
+      <c r="E11" s="51">
         <v>3.89</v>
       </c>
-      <c r="F11" s="55">
-        <v>16863.900000000001</v>
-      </c>
-      <c r="G11" s="56">
+      <c r="F11" s="51">
+        <v>16933.900000000001</v>
+      </c>
+      <c r="G11" s="52">
         <f>F11+70</f>
-        <v>16933.900000000001</v>
-      </c>
-      <c r="H11" s="57">
-        <v>0</v>
-      </c>
-      <c r="I11" s="58">
+        <v>17003.900000000001</v>
+      </c>
+      <c r="H11" s="53">
+        <v>0</v>
+      </c>
+      <c r="I11" s="54">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J11" s="58">
+      <c r="J11" s="54">
         <f>(G11-F11)*93.78</f>
         <v>6564.6</v>
       </c>
-      <c r="K11" s="59">
+      <c r="K11" s="55">
         <f t="shared" ref="K11:K25" si="2">G11-F11</f>
         <v>70</v>
       </c>
-      <c r="L11" s="57">
+      <c r="L11" s="53">
         <f>L9*E11/100</f>
-        <v>15980.504184180023</v>
-      </c>
-      <c r="M11" s="57">
+        <v>9210.6867230999778</v>
+      </c>
+      <c r="M11" s="53">
         <f t="shared" ref="M11:M24" si="3">J11+L11+1</f>
-        <v>22546.104184180025</v>
+        <v>15776.286723099978</v>
       </c>
       <c r="N11" s="22" t="e">
         <f t="shared" ref="N11:N33" si="4">J11/C9*100</f>
@@ -1309,11 +1307,11 @@
       </c>
       <c r="O11" s="23">
         <f>L11/L9*100</f>
-        <v>3.8900000000000006</v>
+        <v>3.8899999999999997</v>
       </c>
       <c r="P11" s="20">
         <f>C7*O11/100</f>
-        <v>3036.1450000000004</v>
+        <v>3036.145</v>
       </c>
       <c r="Q11" s="24">
         <v>0.19</v>
@@ -1325,50 +1323,50 @@
       <c r="U11" s="33"/>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A12" s="43">
+      <c r="A12" s="40">
         <v>3</v>
       </c>
-      <c r="B12" s="43">
+      <c r="B12" s="36">
         <v>3</v>
       </c>
-      <c r="C12" s="43" t="s">
+      <c r="C12" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="43" t="s">
+      <c r="D12" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="43">
+      <c r="E12" s="36">
         <v>4</v>
       </c>
-      <c r="F12" s="43">
-        <v>11246.3</v>
-      </c>
-      <c r="G12" s="41">
+      <c r="F12" s="36">
+        <v>11331.3</v>
+      </c>
+      <c r="G12" s="56">
         <f>F12+85</f>
-        <v>11331.3</v>
-      </c>
-      <c r="H12" s="44">
-        <v>0</v>
-      </c>
-      <c r="I12" s="45">
+        <v>11416.3</v>
+      </c>
+      <c r="H12" s="37">
+        <v>0</v>
+      </c>
+      <c r="I12" s="38">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J12" s="45">
+      <c r="J12" s="38">
         <f t="shared" ref="J12:J33" si="5">(G12-F12)*93.78</f>
         <v>7971.3</v>
       </c>
-      <c r="K12" s="46">
+      <c r="K12" s="39">
         <f>G12-F12</f>
         <v>85</v>
       </c>
-      <c r="L12" s="44">
+      <c r="L12" s="37">
         <f>L9*E12/100</f>
-        <v>16432.395048000024</v>
-      </c>
-      <c r="M12" s="44">
+        <v>9471.1431599999778</v>
+      </c>
+      <c r="M12" s="37">
         <f t="shared" si="3"/>
-        <v>24404.695048000023</v>
+        <v>17443.443159999977</v>
       </c>
       <c r="N12" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1376,11 +1374,11 @@
       </c>
       <c r="O12" s="23">
         <f>J12/L9*100</f>
-        <v>1.9403866512983283</v>
+        <v>3.3665629862573079</v>
       </c>
       <c r="P12" s="20">
         <f>C7*O12/100</f>
-        <v>1514.4717813383454</v>
+        <v>2627.6024107738285</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.25">
@@ -1400,10 +1398,10 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="F13" s="18">
-        <v>26917.4</v>
-      </c>
-      <c r="G13" s="41">
         <v>27384.3</v>
+      </c>
+      <c r="G13" s="57">
+        <v>28103</v>
       </c>
       <c r="H13" s="26">
         <v>0</v>
@@ -1414,19 +1412,19 @@
       </c>
       <c r="J13" s="20">
         <f t="shared" si="5"/>
-        <v>43785.881999999794</v>
+        <v>67399.686000000074</v>
       </c>
       <c r="K13" s="21">
         <f t="shared" si="2"/>
-        <v>466.89999999999782</v>
+        <v>718.70000000000073</v>
       </c>
       <c r="L13" s="19">
         <f>L9*E13/100</f>
-        <v>20129.683933800032</v>
+        <v>11602.150370999972</v>
       </c>
       <c r="M13" s="19">
         <f t="shared" si="3"/>
-        <v>63916.565933799822</v>
+        <v>79002.836371000041</v>
       </c>
       <c r="N13" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1434,57 +1432,57 @@
       </c>
       <c r="O13" s="23">
         <f>J13/L9*100</f>
-        <v>10.658429735190415</v>
+        <v>28.465280214389761</v>
       </c>
       <c r="P13" s="20">
         <f>C7*O13/100</f>
-        <v>8318.9044083161189</v>
+        <v>22217.151207331208</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="18">
         <v>5</v>
       </c>
-      <c r="B14" s="43">
+      <c r="B14" s="40">
         <v>5</v>
       </c>
-      <c r="C14" s="43" t="s">
+      <c r="C14" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="43" t="s">
+      <c r="D14" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="E14" s="43">
+      <c r="E14" s="40">
         <v>3.89</v>
       </c>
-      <c r="F14" s="43">
-        <v>5452.6</v>
-      </c>
-      <c r="G14" s="41">
+      <c r="F14" s="40">
         <v>5693</v>
       </c>
+      <c r="G14" s="57">
+        <v>6130.2</v>
+      </c>
       <c r="H14" s="26">
         <v>0</v>
       </c>
-      <c r="I14" s="45">
+      <c r="I14" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J14" s="45">
+      <c r="J14" s="42">
         <f t="shared" si="5"/>
-        <v>22544.711999999967</v>
-      </c>
-      <c r="K14" s="46">
+        <v>41000.61599999998</v>
+      </c>
+      <c r="K14" s="43">
         <f t="shared" si="2"/>
-        <v>240.39999999999964</v>
-      </c>
-      <c r="L14" s="44">
+        <v>437.19999999999982</v>
+      </c>
+      <c r="L14" s="41">
         <f>L9*E14/100</f>
-        <v>15980.504184180023</v>
-      </c>
-      <c r="M14" s="44">
+        <v>9210.6867230999778</v>
+      </c>
+      <c r="M14" s="41">
         <f t="shared" si="3"/>
-        <v>38526.21618417999</v>
+        <v>50212.302723099958</v>
       </c>
       <c r="N14" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1492,75 +1490,75 @@
       </c>
       <c r="O14" s="23">
         <f>J14/L9*100</f>
-        <v>5.4878700114366765</v>
+        <v>17.316015736372872</v>
       </c>
       <c r="P14" s="20">
         <f>C7*O14/100</f>
-        <v>4283.2825439263261</v>
+        <v>13515.150282239027</v>
       </c>
       <c r="R14">
         <v>2540.8200000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A15" s="18">
+    <row r="15" spans="1:25" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="40">
         <v>6</v>
       </c>
-      <c r="B15" s="37">
+      <c r="B15" s="40">
         <v>6</v>
       </c>
-      <c r="C15" s="37" t="s">
+      <c r="C15" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="37" t="s">
+      <c r="D15" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="E15" s="37">
+      <c r="E15" s="40">
         <v>4</v>
       </c>
-      <c r="F15" s="37">
-        <v>12816.7</v>
-      </c>
-      <c r="G15" s="42">
+      <c r="F15" s="40">
+        <v>13086.7</v>
+      </c>
+      <c r="G15" s="57">
         <f>F15+270</f>
-        <v>13086.7</v>
-      </c>
-      <c r="H15" s="38">
-        <v>0</v>
-      </c>
-      <c r="I15" s="39">
+        <v>13356.7</v>
+      </c>
+      <c r="H15" s="41">
+        <v>0</v>
+      </c>
+      <c r="I15" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J15" s="39">
+      <c r="J15" s="42">
         <f t="shared" si="5"/>
         <v>25320.6</v>
       </c>
-      <c r="K15" s="40">
+      <c r="K15" s="43">
         <f t="shared" si="2"/>
         <v>270</v>
       </c>
-      <c r="L15" s="38">
+      <c r="L15" s="41">
         <f>L9*E15/100</f>
-        <v>16432.395048000024</v>
-      </c>
-      <c r="M15" s="38">
+        <v>9471.1431599999778</v>
+      </c>
+      <c r="M15" s="41">
         <f t="shared" si="3"/>
-        <v>41753.995048000026</v>
-      </c>
-      <c r="N15" s="22" t="e">
+        <v>34792.743159999976</v>
+      </c>
+      <c r="N15" s="59" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="O15" s="23">
+      <c r="O15" s="60">
         <f>J15/L9*100</f>
-        <v>6.1635811276535133</v>
-      </c>
-      <c r="P15" s="20">
+        <v>10.693788309287919</v>
+      </c>
+      <c r="P15" s="42">
         <f>C7*O15/100</f>
-        <v>4810.6750701335668</v>
-      </c>
-      <c r="Y15" s="36"/>
+        <v>8346.5017753992215</v>
+      </c>
+      <c r="Y15" s="62"/>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="18">
@@ -1579,10 +1577,10 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="F16" s="18">
-        <v>17767</v>
-      </c>
-      <c r="G16" s="41">
         <v>17970.599999999999</v>
+      </c>
+      <c r="G16" s="57">
+        <v>18568</v>
       </c>
       <c r="H16" s="19">
         <v>0</v>
@@ -1593,19 +1591,19 @@
       </c>
       <c r="J16" s="20">
         <f t="shared" si="5"/>
-        <v>19093.607999999866</v>
+        <v>56024.172000000137</v>
       </c>
       <c r="K16" s="21">
         <f t="shared" si="2"/>
-        <v>203.59999999999854</v>
+        <v>597.40000000000146</v>
       </c>
       <c r="L16" s="19">
         <f>L9*E16/100</f>
-        <v>20129.683933800032</v>
+        <v>11602.150370999972</v>
       </c>
       <c r="M16" s="19">
         <f t="shared" si="3"/>
-        <v>39224.291933799897</v>
+        <v>67627.322371000104</v>
       </c>
       <c r="N16" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1613,11 +1611,11 @@
       </c>
       <c r="O16" s="23">
         <f>J16/L9*100</f>
-        <v>4.6477967318157276</v>
+        <v>23.660996799883772</v>
       </c>
       <c r="P16" s="20">
         <f>C7*O16/100</f>
-        <v>3627.6053491821749</v>
+        <v>18467.408002309283</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
@@ -1637,10 +1635,10 @@
         <v>3.89</v>
       </c>
       <c r="F17" s="18">
-        <v>5855.11</v>
-      </c>
-      <c r="G17" s="41">
         <v>5950.95</v>
+      </c>
+      <c r="G17" s="57">
+        <v>6108.1</v>
       </c>
       <c r="H17" s="26">
         <v>0</v>
@@ -1651,19 +1649,19 @@
       </c>
       <c r="J17" s="20">
         <f t="shared" si="5"/>
-        <v>8987.8752000000131</v>
+        <v>14737.527000000051</v>
       </c>
       <c r="K17" s="21">
         <f t="shared" si="2"/>
-        <v>95.840000000000146</v>
+        <v>157.15000000000055</v>
       </c>
       <c r="L17" s="19">
         <f>L9*E17/100</f>
-        <v>15980.504184180023</v>
+        <v>9210.6867230999778</v>
       </c>
       <c r="M17" s="19">
         <f t="shared" si="3"/>
-        <v>24969.379384180036</v>
+        <v>23949.213723100031</v>
       </c>
       <c r="N17" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1671,57 +1669,57 @@
       </c>
       <c r="O17" s="23">
         <f>J17/L9*100</f>
-        <v>2.1878430195344949</v>
+        <v>6.2241808622392671</v>
       </c>
       <c r="P17" s="20">
         <f>C7*O17/100</f>
-        <v>1707.6114767466734</v>
+        <v>4857.973162977748</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="18">
         <v>9</v>
       </c>
-      <c r="B18" s="43">
+      <c r="B18" s="40">
         <v>9</v>
       </c>
-      <c r="C18" s="43" t="s">
+      <c r="C18" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="43" t="s">
+      <c r="D18" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="E18" s="43">
+      <c r="E18" s="40">
         <v>4</v>
       </c>
-      <c r="F18" s="43">
-        <v>19713.599999999999</v>
-      </c>
-      <c r="G18" s="41">
+      <c r="F18" s="40">
         <v>19975.5</v>
       </c>
-      <c r="H18" s="53">
-        <v>0</v>
-      </c>
-      <c r="I18" s="45">
+      <c r="G18" s="57">
+        <v>20633.2</v>
+      </c>
+      <c r="H18" s="49">
+        <v>0</v>
+      </c>
+      <c r="I18" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J18" s="45">
+      <c r="J18" s="42">
         <f t="shared" si="5"/>
-        <v>24560.982000000138</v>
-      </c>
-      <c r="K18" s="46">
+        <v>61679.106000000073</v>
+      </c>
+      <c r="K18" s="43">
         <f t="shared" si="2"/>
-        <v>261.90000000000146</v>
-      </c>
-      <c r="L18" s="44">
+        <v>657.70000000000073</v>
+      </c>
+      <c r="L18" s="41">
         <f>L9*E18/100</f>
-        <v>16432.395048000024</v>
-      </c>
-      <c r="M18" s="44">
+        <v>9471.1431599999778</v>
+      </c>
+      <c r="M18" s="41">
         <f t="shared" si="3"/>
-        <v>40994.377048000162</v>
+        <v>71151.24916000005</v>
       </c>
       <c r="N18" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1729,57 +1727,57 @@
       </c>
       <c r="O18" s="23">
         <f>J18/L9*100</f>
-        <v>5.978673693823942</v>
+        <v>26.049276188958046</v>
       </c>
       <c r="P18" s="20">
         <f>C7*O18/100</f>
-        <v>4666.3548180295866</v>
+        <v>20331.460065481755</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="18">
         <v>10</v>
       </c>
-      <c r="B19" s="48">
+      <c r="B19" s="45">
         <v>10</v>
       </c>
-      <c r="C19" s="48" t="s">
+      <c r="C19" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="D19" s="48" t="s">
+      <c r="D19" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="E19" s="48">
+      <c r="E19" s="45">
         <v>12.66</v>
       </c>
-      <c r="F19" s="48">
-        <v>22979.4</v>
-      </c>
-      <c r="G19" s="52">
+      <c r="F19" s="45">
         <v>23140.400000000001</v>
       </c>
-      <c r="H19" s="51">
-        <v>0</v>
-      </c>
-      <c r="I19" s="49">
+      <c r="G19" s="58">
+        <v>23373.9</v>
+      </c>
+      <c r="H19" s="48">
+        <v>0</v>
+      </c>
+      <c r="I19" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J19" s="49">
+      <c r="J19" s="46">
         <f t="shared" si="5"/>
-        <v>15098.58</v>
-      </c>
-      <c r="K19" s="50">
+        <v>21897.63</v>
+      </c>
+      <c r="K19" s="47">
         <f t="shared" si="2"/>
-        <v>161</v>
-      </c>
-      <c r="L19" s="51">
+        <v>233.5</v>
+      </c>
+      <c r="L19" s="48">
         <f>L9*E19/100</f>
-        <v>52008.530326920074</v>
-      </c>
-      <c r="M19" s="51">
+        <v>29976.168101399933</v>
+      </c>
+      <c r="M19" s="48">
         <f>J19+L19+1</f>
-        <v>67108.110326920068</v>
+        <v>51874.798101399938</v>
       </c>
       <c r="N19" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1787,58 +1785,58 @@
       </c>
       <c r="O19" s="23">
         <f>J19/L9*100</f>
-        <v>3.6753205983415396</v>
+        <v>9.2481465563656631</v>
       </c>
       <c r="P19" s="20">
         <f>C7*O19/100</f>
-        <v>2868.5877270055712</v>
+        <v>7218.1783872433998</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A20" s="43">
+      <c r="A20" s="40">
         <v>11</v>
       </c>
-      <c r="B20" s="43">
+      <c r="B20" s="40">
         <v>11</v>
       </c>
-      <c r="C20" s="43" t="s">
+      <c r="C20" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="D20" s="43" t="s">
+      <c r="D20" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="E20" s="43">
+      <c r="E20" s="40">
         <v>7.75</v>
       </c>
-      <c r="F20" s="43">
-        <v>17545.099999999999</v>
-      </c>
-      <c r="G20" s="41">
+      <c r="F20" s="40">
+        <v>17745.099999999999</v>
+      </c>
+      <c r="G20" s="57">
         <f>F20+200</f>
-        <v>17745.099999999999</v>
+        <v>17945.099999999999</v>
       </c>
       <c r="H20" s="26">
         <v>0</v>
       </c>
-      <c r="I20" s="45">
+      <c r="I20" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J20" s="45">
+      <c r="J20" s="42">
         <f t="shared" si="5"/>
         <v>18756</v>
       </c>
-      <c r="K20" s="46">
+      <c r="K20" s="43">
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
-      <c r="L20" s="44">
+      <c r="L20" s="41">
         <f>L9*E20/100</f>
-        <v>31837.765405500046</v>
-      </c>
-      <c r="M20" s="44">
+        <v>18350.339872499957</v>
+      </c>
+      <c r="M20" s="41">
         <f t="shared" si="3"/>
-        <v>50594.765405500046</v>
+        <v>37107.339872499957</v>
       </c>
       <c r="N20" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1846,57 +1844,57 @@
       </c>
       <c r="O20" s="23">
         <f>J20/L9*100</f>
-        <v>4.5656156501137142</v>
+        <v>7.9213246735466063</v>
       </c>
       <c r="P20" s="20">
         <f>C7*O20/100</f>
-        <v>3563.4630149137538</v>
+        <v>6182.5939077031262</v>
       </c>
     </row>
     <row r="21" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="37">
+      <c r="A21" s="36">
         <v>12</v>
       </c>
-      <c r="B21" s="43">
+      <c r="B21" s="40">
         <v>12</v>
       </c>
-      <c r="C21" s="43" t="s">
+      <c r="C21" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="54" t="s">
+      <c r="D21" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="E21" s="43">
+      <c r="E21" s="40">
         <v>7.51</v>
       </c>
-      <c r="F21" s="43">
-        <v>14348.5</v>
-      </c>
-      <c r="G21" s="41">
+      <c r="F21" s="40">
         <v>14594.4</v>
       </c>
+      <c r="G21" s="57">
+        <v>15067</v>
+      </c>
       <c r="H21" s="26">
         <v>0</v>
       </c>
-      <c r="I21" s="45">
+      <c r="I21" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J21" s="45">
+      <c r="J21" s="42">
         <f t="shared" si="5"/>
-        <v>23060.501999999968</v>
-      </c>
-      <c r="K21" s="46">
+        <v>44320.428000000036</v>
+      </c>
+      <c r="K21" s="43">
         <f t="shared" si="2"/>
-        <v>245.89999999999964</v>
-      </c>
-      <c r="L21" s="44">
+        <v>472.60000000000036</v>
+      </c>
+      <c r="L21" s="41">
         <f>L9*E21/100</f>
-        <v>30851.821702620044</v>
-      </c>
-      <c r="M21" s="44">
+        <v>17782.071282899957</v>
+      </c>
+      <c r="M21" s="41">
         <f t="shared" si="3"/>
-        <v>53913.323702620008</v>
+        <v>62103.499282899997</v>
       </c>
       <c r="N21" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1904,62 +1902,62 @@
       </c>
       <c r="O21" s="23">
         <f>J21/L9*100</f>
-        <v>5.6134244418148036</v>
+        <v>18.718090203590645</v>
       </c>
       <c r="P21" s="20">
         <f>C7*O21/100</f>
-        <v>4381.277776836454</v>
+        <v>14609.4694039025</v>
       </c>
       <c r="S21">
         <f>G21-F21</f>
-        <v>245.89999999999964</v>
+        <v>472.60000000000036</v>
       </c>
     </row>
     <row r="22" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="43">
+      <c r="A22" s="40">
         <v>13</v>
       </c>
-      <c r="B22" s="55">
+      <c r="B22" s="40">
         <v>13</v>
       </c>
-      <c r="C22" s="55" t="s">
+      <c r="C22" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="D22" s="55" t="s">
+      <c r="D22" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="E22" s="55">
+      <c r="E22" s="40">
         <v>4.45</v>
       </c>
-      <c r="F22" s="55">
-        <v>10672.2</v>
-      </c>
-      <c r="G22" s="56">
-        <f>F22+193-30</f>
+      <c r="F22" s="40">
         <v>10835.2</v>
       </c>
-      <c r="H22" s="60">
-        <v>0</v>
-      </c>
-      <c r="I22" s="58">
+      <c r="G22" s="57">
+        <f>F22+193</f>
+        <v>11028.2</v>
+      </c>
+      <c r="H22" s="26">
+        <v>0</v>
+      </c>
+      <c r="I22" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J22" s="58">
+      <c r="J22" s="42">
         <f t="shared" si="5"/>
-        <v>15286.14</v>
-      </c>
-      <c r="K22" s="59">
+        <v>18099.54</v>
+      </c>
+      <c r="K22" s="43">
         <f t="shared" si="2"/>
-        <v>163</v>
-      </c>
-      <c r="L22" s="57">
+        <v>193</v>
+      </c>
+      <c r="L22" s="41">
         <f>L9*E22/100</f>
-        <v>18281.039490900024</v>
-      </c>
-      <c r="M22" s="57">
+        <v>10536.646765499976</v>
+      </c>
+      <c r="M22" s="41">
         <f t="shared" si="3"/>
-        <v>33568.179490900024</v>
+        <v>28637.186765499977</v>
       </c>
       <c r="N22" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1967,61 +1965,61 @@
       </c>
       <c r="O22" s="23">
         <f>J22/L9*100</f>
-        <v>3.7209767548426766</v>
+        <v>7.6440783099724756</v>
       </c>
       <c r="P22" s="20">
         <f>C7*O22/100</f>
-        <v>2904.2223571547092</v>
+        <v>5966.2031209335173</v>
       </c>
       <c r="S22">
         <f>G22-F22</f>
-        <v>163</v>
+        <v>193</v>
       </c>
     </row>
     <row r="23" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="18">
         <v>14</v>
       </c>
-      <c r="B23" s="43">
+      <c r="B23" s="40">
         <v>14</v>
       </c>
-      <c r="C23" s="43" t="s">
+      <c r="C23" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="D23" s="43" t="s">
+      <c r="D23" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="E23" s="43">
+      <c r="E23" s="40">
         <v>6.17</v>
       </c>
-      <c r="F23" s="43">
-        <v>20488.68</v>
-      </c>
-      <c r="G23" s="41">
+      <c r="F23" s="40">
         <v>20525.349999999999</v>
       </c>
-      <c r="H23" s="44">
-        <v>0</v>
-      </c>
-      <c r="I23" s="45">
+      <c r="G23" s="57">
+        <v>20525.349999999999</v>
+      </c>
+      <c r="H23" s="41">
+        <v>0</v>
+      </c>
+      <c r="I23" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J23" s="45">
+      <c r="J23" s="42">
         <f t="shared" si="5"/>
-        <v>3438.9125999998364</v>
-      </c>
-      <c r="K23" s="46">
+        <v>0</v>
+      </c>
+      <c r="K23" s="43">
         <f t="shared" si="2"/>
-        <v>36.669999999998254</v>
-      </c>
-      <c r="L23" s="44">
+        <v>0</v>
+      </c>
+      <c r="L23" s="41">
         <f>L9*E23/100</f>
-        <v>25346.969361540036</v>
-      </c>
-      <c r="M23" s="44">
+        <v>14609.238324299964</v>
+      </c>
+      <c r="M23" s="41">
         <f>J23+L23+1</f>
-        <v>28786.881961539872</v>
+        <v>14610.238324299964</v>
       </c>
       <c r="N23" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2029,57 +2027,57 @@
       </c>
       <c r="O23" s="23">
         <f>J23/L9*100</f>
-        <v>0.83710562944830957</v>
+        <v>0</v>
       </c>
       <c r="P23" s="20">
         <f>C7*O23/100</f>
-        <v>653.36094378440566</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="18">
+      <c r="A24" s="40">
         <v>15</v>
       </c>
-      <c r="B24" s="37">
+      <c r="B24" s="40">
         <v>15</v>
       </c>
-      <c r="C24" s="37" t="s">
+      <c r="C24" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="D24" s="37" t="s">
+      <c r="D24" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="E24" s="37">
+      <c r="E24" s="40">
         <v>4.45</v>
       </c>
-      <c r="F24" s="37">
-        <v>29965.1</v>
-      </c>
-      <c r="G24" s="42">
+      <c r="F24" s="40">
         <v>30195.599999999999</v>
       </c>
-      <c r="H24" s="38">
-        <v>0</v>
-      </c>
-      <c r="I24" s="39">
+      <c r="G24" s="57">
+        <v>30484.400000000001</v>
+      </c>
+      <c r="H24" s="41">
+        <v>0</v>
+      </c>
+      <c r="I24" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J24" s="39">
+      <c r="J24" s="42">
         <f t="shared" si="5"/>
-        <v>21616.29</v>
-      </c>
-      <c r="K24" s="40">
+        <v>27083.664000000274</v>
+      </c>
+      <c r="K24" s="43">
         <f t="shared" si="2"/>
-        <v>230.5</v>
-      </c>
-      <c r="L24" s="38">
+        <v>288.80000000000291</v>
+      </c>
+      <c r="L24" s="41">
         <f>L9*E24/100</f>
-        <v>18281.039490900024</v>
-      </c>
-      <c r="M24" s="38">
+        <v>10536.646765499976</v>
+      </c>
+      <c r="M24" s="41">
         <f t="shared" si="3"/>
-        <v>39898.329490900025</v>
+        <v>37621.310765500253</v>
       </c>
       <c r="N24" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2087,57 +2085,57 @@
       </c>
       <c r="O24" s="23">
         <f>J24/L9*100</f>
-        <v>5.2618720367560554</v>
+        <v>11.438392828601415</v>
       </c>
       <c r="P24" s="20">
         <f>C7*O24/100</f>
-        <v>4106.8911246881007</v>
+        <v>8927.6656027234039</v>
       </c>
     </row>
     <row r="25" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="18">
+      <c r="A25" s="40">
         <v>16</v>
       </c>
-      <c r="B25" s="37">
+      <c r="B25" s="40">
         <v>16</v>
       </c>
-      <c r="C25" s="37" t="s">
+      <c r="C25" s="40" t="s">
         <v>66</v>
       </c>
-      <c r="D25" s="37" t="s">
+      <c r="D25" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="E25" s="37">
+      <c r="E25" s="40">
         <v>9.19</v>
       </c>
-      <c r="F25" s="37">
-        <v>11147.8</v>
-      </c>
-      <c r="G25" s="42">
+      <c r="F25" s="40">
         <v>11291.4</v>
       </c>
-      <c r="H25" s="38">
-        <v>0</v>
-      </c>
-      <c r="I25" s="39">
+      <c r="G25" s="57">
+        <v>11470.8</v>
+      </c>
+      <c r="H25" s="41">
+        <v>0</v>
+      </c>
+      <c r="I25" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J25" s="39">
+      <c r="J25" s="42">
         <f t="shared" si="5"/>
-        <v>13466.808000000034</v>
-      </c>
-      <c r="K25" s="40">
+        <v>16824.131999999965</v>
+      </c>
+      <c r="K25" s="43">
         <f t="shared" si="2"/>
-        <v>143.60000000000036</v>
-      </c>
-      <c r="L25" s="38">
+        <v>179.39999999999964</v>
+      </c>
+      <c r="L25" s="41">
         <f>L9*E25/100</f>
-        <v>37753.427622780051</v>
-      </c>
-      <c r="M25" s="38">
+        <v>21759.951410099948</v>
+      </c>
+      <c r="M25" s="41">
         <f>J25+L25+1</f>
-        <v>51221.235622780085</v>
+        <v>38585.083410099913</v>
       </c>
       <c r="N25" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2145,54 +2143,54 @@
       </c>
       <c r="O25" s="23">
         <f>J25/L9*100</f>
-        <v>3.2781120367816543</v>
+        <v>7.1054282321712918</v>
       </c>
       <c r="P25" s="20">
         <f>C7*O25/100</f>
-        <v>2558.5664447080812</v>
+        <v>5545.7867352096937</v>
       </c>
     </row>
     <row r="26" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="37">
+      <c r="A26" s="36">
         <v>17</v>
       </c>
-      <c r="B26" s="43">
+      <c r="B26" s="40">
         <v>17</v>
       </c>
-      <c r="C26" s="43" t="s">
+      <c r="C26" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="D26" s="43" t="s">
+      <c r="D26" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="E26" s="43">
+      <c r="E26" s="40">
         <v>1.18</v>
       </c>
-      <c r="F26" s="43">
-        <v>0</v>
-      </c>
-      <c r="G26" s="43">
-        <v>0</v>
-      </c>
-      <c r="H26" s="44">
-        <v>0</v>
-      </c>
-      <c r="I26" s="45">
+      <c r="F26" s="40">
+        <v>0</v>
+      </c>
+      <c r="G26" s="40">
+        <v>0</v>
+      </c>
+      <c r="H26" s="41">
+        <v>0</v>
+      </c>
+      <c r="I26" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J26" s="45">
+      <c r="J26" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K26" s="44"/>
-      <c r="L26" s="44">
+      <c r="K26" s="41"/>
+      <c r="L26" s="41">
         <f>L9*E26/100</f>
-        <v>4847.5565391600067</v>
-      </c>
-      <c r="M26" s="44">
+        <v>2793.9872321999933</v>
+      </c>
+      <c r="M26" s="41">
         <f t="shared" ref="M26:M33" si="6">J26+L26</f>
-        <v>4847.5565391600067</v>
+        <v>2793.9872321999933</v>
       </c>
       <c r="N26" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2211,43 +2209,43 @@
       <c r="A27" s="18">
         <v>18</v>
       </c>
-      <c r="B27" s="37">
+      <c r="B27" s="36">
         <v>18</v>
       </c>
-      <c r="C27" s="37" t="s">
+      <c r="C27" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="D27" s="37" t="s">
+      <c r="D27" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="E27" s="37">
+      <c r="E27" s="36">
         <v>1.18</v>
       </c>
-      <c r="F27" s="37">
-        <v>0</v>
-      </c>
-      <c r="G27" s="37">
-        <v>0</v>
-      </c>
-      <c r="H27" s="38">
-        <v>0</v>
-      </c>
-      <c r="I27" s="39">
+      <c r="F27" s="36">
+        <v>0</v>
+      </c>
+      <c r="G27" s="36">
+        <v>0</v>
+      </c>
+      <c r="H27" s="37">
+        <v>0</v>
+      </c>
+      <c r="I27" s="38">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J27" s="39">
+      <c r="J27" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K27" s="38"/>
-      <c r="L27" s="38">
+      <c r="K27" s="37"/>
+      <c r="L27" s="37">
         <f>L26</f>
-        <v>4847.5565391600067</v>
-      </c>
-      <c r="M27" s="38">
+        <v>2793.9872321999933</v>
+      </c>
+      <c r="M27" s="37">
         <f t="shared" si="6"/>
-        <v>4847.5565391600067</v>
+        <v>2793.9872321999933</v>
       </c>
       <c r="N27" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2266,43 +2264,43 @@
       <c r="A28" s="18">
         <v>19</v>
       </c>
-      <c r="B28" s="37">
+      <c r="B28" s="36">
         <v>19</v>
       </c>
-      <c r="C28" s="37" t="s">
+      <c r="C28" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="D28" s="37" t="s">
+      <c r="D28" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="E28" s="37">
+      <c r="E28" s="36">
         <v>1.18</v>
       </c>
-      <c r="F28" s="37">
-        <v>0</v>
-      </c>
-      <c r="G28" s="37">
-        <v>0</v>
-      </c>
-      <c r="H28" s="38">
-        <v>0</v>
-      </c>
-      <c r="I28" s="39">
+      <c r="F28" s="36">
+        <v>0</v>
+      </c>
+      <c r="G28" s="36">
+        <v>0</v>
+      </c>
+      <c r="H28" s="37">
+        <v>0</v>
+      </c>
+      <c r="I28" s="38">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J28" s="39">
+      <c r="J28" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K28" s="38"/>
-      <c r="L28" s="38">
+      <c r="K28" s="37"/>
+      <c r="L28" s="37">
         <f>L27</f>
-        <v>4847.5565391600067</v>
-      </c>
-      <c r="M28" s="38">
+        <v>2793.9872321999933</v>
+      </c>
+      <c r="M28" s="37">
         <f t="shared" si="6"/>
-        <v>4847.5565391600067</v>
+        <v>2793.9872321999933</v>
       </c>
       <c r="N28" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2318,46 +2316,46 @@
       </c>
     </row>
     <row r="29" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="43">
+      <c r="A29" s="40">
         <v>20</v>
       </c>
-      <c r="B29" s="43">
+      <c r="B29" s="36">
         <v>20</v>
       </c>
-      <c r="C29" s="43" t="s">
+      <c r="C29" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="D29" s="43" t="s">
+      <c r="D29" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="E29" s="43">
+      <c r="E29" s="36">
         <v>1.18</v>
       </c>
-      <c r="F29" s="43">
-        <v>0</v>
-      </c>
-      <c r="G29" s="43">
-        <v>0</v>
-      </c>
-      <c r="H29" s="44">
-        <v>0</v>
-      </c>
-      <c r="I29" s="45">
+      <c r="F29" s="36">
+        <v>0</v>
+      </c>
+      <c r="G29" s="36">
+        <v>0</v>
+      </c>
+      <c r="H29" s="37">
+        <v>0</v>
+      </c>
+      <c r="I29" s="38">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J29" s="45">
+      <c r="J29" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K29" s="44"/>
-      <c r="L29" s="44">
+      <c r="K29" s="37"/>
+      <c r="L29" s="37">
         <f>L28</f>
-        <v>4847.5565391600067</v>
-      </c>
-      <c r="M29" s="44">
+        <v>2793.9872321999933</v>
+      </c>
+      <c r="M29" s="37">
         <f t="shared" si="6"/>
-        <v>4847.5565391600067</v>
+        <v>2793.9872321999933</v>
       </c>
       <c r="N29" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2382,7 +2380,7 @@
       <c r="C30" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D30" s="48" t="s">
+      <c r="D30" s="45" t="s">
         <v>63</v>
       </c>
       <c r="E30" s="18">
@@ -2408,11 +2406,11 @@
       <c r="K30" s="19"/>
       <c r="L30" s="19">
         <f t="shared" ref="L30:L33" si="7">L29</f>
-        <v>4847.5565391600067</v>
+        <v>2793.9872321999933</v>
       </c>
       <c r="M30" s="19">
         <f t="shared" si="6"/>
-        <v>4847.5565391600067</v>
+        <v>2793.9872321999933</v>
       </c>
       <c r="N30" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2463,11 +2461,11 @@
       <c r="K31" s="19"/>
       <c r="L31" s="19">
         <f t="shared" si="7"/>
-        <v>4847.5565391600067</v>
+        <v>2793.9872321999933</v>
       </c>
       <c r="M31" s="19">
         <f t="shared" si="6"/>
-        <v>4847.5565391600067</v>
+        <v>2793.9872321999933</v>
       </c>
       <c r="N31" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2483,46 +2481,46 @@
       </c>
     </row>
     <row r="32" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="37">
+      <c r="A32" s="36">
         <v>23</v>
       </c>
-      <c r="B32" s="43">
+      <c r="B32" s="40">
         <v>23</v>
       </c>
-      <c r="C32" s="43" t="s">
+      <c r="C32" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="D32" s="43" t="s">
+      <c r="D32" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="E32" s="43">
+      <c r="E32" s="40">
         <v>1.18</v>
       </c>
-      <c r="F32" s="43">
-        <v>0</v>
-      </c>
-      <c r="G32" s="43">
-        <v>0</v>
-      </c>
-      <c r="H32" s="44">
-        <v>0</v>
-      </c>
-      <c r="I32" s="45">
+      <c r="F32" s="40">
+        <v>0</v>
+      </c>
+      <c r="G32" s="40">
+        <v>0</v>
+      </c>
+      <c r="H32" s="41">
+        <v>0</v>
+      </c>
+      <c r="I32" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J32" s="45">
+      <c r="J32" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K32" s="44"/>
-      <c r="L32" s="44">
+      <c r="K32" s="41"/>
+      <c r="L32" s="41">
         <f t="shared" si="7"/>
-        <v>4847.5565391600067</v>
-      </c>
-      <c r="M32" s="44">
+        <v>2793.9872321999933</v>
+      </c>
+      <c r="M32" s="41">
         <f t="shared" si="6"/>
-        <v>4847.5565391600067</v>
+        <v>2793.9872321999933</v>
       </c>
       <c r="N32" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2538,46 +2536,46 @@
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" s="43">
+      <c r="A33" s="40">
         <v>24</v>
       </c>
-      <c r="B33" s="43">
+      <c r="B33" s="40">
         <v>24</v>
       </c>
-      <c r="C33" s="43" t="s">
+      <c r="C33" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="D33" s="54" t="s">
+      <c r="D33" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="E33" s="43">
+      <c r="E33" s="40">
         <v>1.18</v>
       </c>
-      <c r="F33" s="43">
-        <v>0</v>
-      </c>
-      <c r="G33" s="43">
-        <v>0</v>
-      </c>
-      <c r="H33" s="44">
-        <v>0</v>
-      </c>
-      <c r="I33" s="45">
+      <c r="F33" s="40">
+        <v>0</v>
+      </c>
+      <c r="G33" s="40">
+        <v>0</v>
+      </c>
+      <c r="H33" s="41">
+        <v>0</v>
+      </c>
+      <c r="I33" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J33" s="45">
+      <c r="J33" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K33" s="44"/>
-      <c r="L33" s="44">
+      <c r="K33" s="41"/>
+      <c r="L33" s="41">
         <f t="shared" si="7"/>
-        <v>4847.5565391600067</v>
-      </c>
-      <c r="M33" s="44">
+        <v>2793.9872321999933</v>
+      </c>
+      <c r="M33" s="41">
         <f t="shared" si="6"/>
-        <v>4847.5565391600067</v>
+        <v>2793.9872321999933</v>
       </c>
       <c r="N33" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2609,19 +2607,19 @@
       </c>
       <c r="J34" s="30">
         <f>SUM(J10:J33)</f>
-        <v>297583.63379999943</v>
+        <v>471614.93100000056</v>
       </c>
       <c r="K34" s="29">
         <f>SUM(K10:K33)</f>
-        <v>3173.2099999999937</v>
+        <v>5028.9500000000062</v>
       </c>
       <c r="L34" s="29">
         <f>SUM(L10:L33)</f>
-        <v>410768.79521238065</v>
+        <v>236754.90114209941</v>
       </c>
       <c r="M34" s="29">
         <f>SUM(M10:M33)</f>
-        <v>708370.42901237961</v>
+        <v>708387.83214210009</v>
       </c>
       <c r="N34" s="5"/>
       <c r="O34" s="2" t="e">
@@ -2633,19 +2631,19 @@
       <c r="A35" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="C35" s="64" t="s">
+      <c r="C35" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="D35" s="62"/>
-      <c r="E35" s="62"/>
-      <c r="F35" s="62"/>
-      <c r="G35" s="62"/>
-      <c r="H35" s="62"/>
-      <c r="I35" s="62"/>
-      <c r="J35" s="62"/>
-      <c r="K35" s="62"/>
-      <c r="L35" s="62"/>
-      <c r="M35" s="65"/>
+      <c r="D35" s="65"/>
+      <c r="E35" s="65"/>
+      <c r="F35" s="65"/>
+      <c r="G35" s="65"/>
+      <c r="H35" s="65"/>
+      <c r="I35" s="65"/>
+      <c r="J35" s="65"/>
+      <c r="K35" s="65"/>
+      <c r="L35" s="65"/>
+      <c r="M35" s="68"/>
       <c r="N35" s="31"/>
       <c r="O35" s="2" t="e">
         <f t="shared" si="9"/>
@@ -2663,86 +2661,86 @@
       <c r="H37" s="5"/>
       <c r="K37" s="34">
         <f>J34+L34</f>
-        <v>708352.42901238007</v>
+        <v>708369.83214209997</v>
       </c>
       <c r="L37" s="34"/>
       <c r="O37" s="2"/>
     </row>
-    <row r="38" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="66" t="s">
+    <row r="38" spans="1:16" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="69" t="s">
         <v>65</v>
       </c>
-      <c r="C38" s="67"/>
-      <c r="D38" s="67"/>
-      <c r="E38" s="67"/>
-      <c r="F38" s="67"/>
-      <c r="G38" s="67"/>
-      <c r="H38" s="67"/>
-      <c r="I38" s="67"/>
-      <c r="J38" s="67"/>
-      <c r="K38" s="67"/>
-      <c r="L38" s="67"/>
-      <c r="M38" s="67"/>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="70"/>
+      <c r="K38" s="70"/>
+      <c r="L38" s="70"/>
+      <c r="M38" s="70"/>
       <c r="O38" s="2"/>
     </row>
-    <row r="39" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="67"/>
-      <c r="C39" s="67"/>
-      <c r="D39" s="67"/>
-      <c r="E39" s="67"/>
-      <c r="F39" s="67"/>
-      <c r="G39" s="67"/>
-      <c r="H39" s="67"/>
-      <c r="I39" s="67"/>
-      <c r="J39" s="67"/>
-      <c r="K39" s="67"/>
-      <c r="L39" s="67"/>
-      <c r="M39" s="67"/>
+    <row r="39" spans="1:16" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="70"/>
+      <c r="C39" s="70"/>
+      <c r="D39" s="70"/>
+      <c r="E39" s="70"/>
+      <c r="F39" s="70"/>
+      <c r="G39" s="70"/>
+      <c r="H39" s="70"/>
+      <c r="I39" s="70"/>
+      <c r="J39" s="70"/>
+      <c r="K39" s="70"/>
+      <c r="L39" s="70"/>
+      <c r="M39" s="70"/>
       <c r="O39" s="2"/>
     </row>
-    <row r="40" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="67"/>
-      <c r="C40" s="67"/>
-      <c r="D40" s="67"/>
-      <c r="E40" s="67"/>
-      <c r="F40" s="67"/>
-      <c r="G40" s="67"/>
-      <c r="H40" s="67"/>
-      <c r="I40" s="67"/>
-      <c r="J40" s="67"/>
-      <c r="K40" s="67"/>
-      <c r="L40" s="67"/>
-      <c r="M40" s="67"/>
+    <row r="40" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="70"/>
+      <c r="C40" s="70"/>
+      <c r="D40" s="70"/>
+      <c r="E40" s="70"/>
+      <c r="F40" s="70"/>
+      <c r="G40" s="70"/>
+      <c r="H40" s="70"/>
+      <c r="I40" s="70"/>
+      <c r="J40" s="70"/>
+      <c r="K40" s="70"/>
+      <c r="L40" s="70"/>
+      <c r="M40" s="70"/>
       <c r="O40" s="2"/>
     </row>
-    <row r="41" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="67"/>
-      <c r="C41" s="67"/>
-      <c r="D41" s="67"/>
-      <c r="E41" s="67"/>
-      <c r="F41" s="67"/>
-      <c r="G41" s="67"/>
-      <c r="H41" s="67"/>
-      <c r="I41" s="67"/>
-      <c r="J41" s="67"/>
-      <c r="K41" s="67"/>
-      <c r="L41" s="67"/>
-      <c r="M41" s="67"/>
+    <row r="41" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="70"/>
+      <c r="C41" s="70"/>
+      <c r="D41" s="70"/>
+      <c r="E41" s="70"/>
+      <c r="F41" s="70"/>
+      <c r="G41" s="70"/>
+      <c r="H41" s="70"/>
+      <c r="I41" s="70"/>
+      <c r="J41" s="70"/>
+      <c r="K41" s="70"/>
+      <c r="L41" s="70"/>
+      <c r="M41" s="70"/>
       <c r="O41" s="2"/>
     </row>
-    <row r="42" spans="1:16" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="67"/>
-      <c r="C42" s="67"/>
-      <c r="D42" s="67"/>
-      <c r="E42" s="67"/>
-      <c r="F42" s="67"/>
-      <c r="G42" s="67"/>
-      <c r="H42" s="67"/>
-      <c r="I42" s="67"/>
-      <c r="J42" s="67"/>
-      <c r="K42" s="67"/>
-      <c r="L42" s="67"/>
-      <c r="M42" s="67"/>
+    <row r="42" spans="1:16" ht="64.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="70"/>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="70"/>
+      <c r="K42" s="70"/>
+      <c r="L42" s="70"/>
+      <c r="M42" s="70"/>
       <c r="O42" s="2"/>
     </row>
     <row r="43" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6614,21 +6612,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="63"/>
+      <c r="A1" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="66"/>
       <c r="N1" s="1"/>
       <c r="O1" s="2"/>
       <c r="P1" s="3"/>
@@ -8220,19 +8218,19 @@
       <c r="A35" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="C35" s="64" t="s">
+      <c r="C35" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="D35" s="62"/>
-      <c r="E35" s="62"/>
-      <c r="F35" s="62"/>
-      <c r="G35" s="62"/>
-      <c r="H35" s="62"/>
-      <c r="I35" s="62"/>
-      <c r="J35" s="62"/>
-      <c r="K35" s="62"/>
-      <c r="L35" s="62"/>
-      <c r="M35" s="65"/>
+      <c r="D35" s="65"/>
+      <c r="E35" s="65"/>
+      <c r="F35" s="65"/>
+      <c r="G35" s="65"/>
+      <c r="H35" s="65"/>
+      <c r="I35" s="65"/>
+      <c r="J35" s="65"/>
+      <c r="K35" s="65"/>
+      <c r="L35" s="65"/>
+      <c r="M35" s="68"/>
       <c r="N35" s="31"/>
       <c r="O35" s="2" t="e">
         <f t="shared" si="8"/>
